--- a/ET-release8.1/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20468320-D0D0-41BC-AE75-4790184486FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2763D59A-9BAC-44F9-9F9D-EA6C4644C852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="5880" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1635" yWindow="3540" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EffectProto" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>#</t>
   </si>
@@ -83,6 +83,33 @@
   </si>
   <si>
     <t>Scale</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_BloodHit</t>
+  </si>
+  <si>
+    <t>DestroyTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>销毁时间(毫秒) -1无限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1,1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -147,13 +174,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -458,24 +488,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:I6"/>
+  <dimension ref="C2:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="28.75" style="2" customWidth="1"/>
-    <col min="7" max="9" width="9.625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
+    <col min="8" max="10" width="9.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="F2" s="2" t="s">
+    <row r="2" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -486,19 +518,25 @@
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="K3" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="4" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -509,19 +547,25 @@
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="K4" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -535,16 +579,22 @@
         <v>7</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="J5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>22001</v>
       </c>
@@ -554,9 +604,21 @@
       <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="1">
+        <v>500</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2763D59A-9BAC-44F9-9F9D-EA6C4644C852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED616AAD-7EED-457A-9097-79A4B7206FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1635" yWindow="3540" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2400" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EffectProto" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>#</t>
   </si>
@@ -50,10 +50,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>测试1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>挂点</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -110,6 +106,25 @@
   </si>
   <si>
     <t>1,1,1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试受击</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试火球</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Fireball</t>
+  </si>
+  <si>
+    <t>测试施法特效</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_CastBegin</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -488,14 +503,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:K6"/>
+  <dimension ref="C2:K8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
     <col min="8" max="10" width="9.625" style="2" customWidth="1"/>
     <col min="11" max="11" width="16.75" style="2" bestFit="1" customWidth="1"/>
@@ -518,22 +533,22 @@
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="3:11" x14ac:dyDescent="0.3">
@@ -547,22 +562,22 @@
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="3:11" x14ac:dyDescent="0.3">
@@ -582,16 +597,16 @@
         <v>7</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.3">
@@ -602,22 +617,74 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="K6" s="1">
         <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C7" s="1">
+        <v>22002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="1">
+        <v>4</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C8" s="1">
+        <v>22003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="1">
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/ET-release8.1/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED616AAD-7EED-457A-9097-79A4B7206FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E241BD9-7486-4206-AE1E-19ACEA83FBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2400" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
   <si>
     <t>#</t>
   </si>
@@ -126,6 +126,13 @@
   <si>
     <t>Effect_CastBegin</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试毒Buff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Posion</t>
   </si>
 </sst>
 </file>
@@ -189,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -198,6 +205,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -503,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C2:K8"/>
+  <dimension ref="C2:K9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -687,6 +697,32 @@
         <v>800</v>
       </c>
     </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="C9" s="1">
+        <v>22004</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="5">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
